--- a/outputs/sitrang/Ablation_Kappa_Comparison/Sitrang_Ablation_Kappa_Comparison.xlsx
+++ b/outputs/sitrang/Ablation_Kappa_Comparison/Sitrang_Ablation_Kappa_Comparison.xlsx
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>25.64102564102564</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>25.64102564102564</v>
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>25.64102564102564</v>
@@ -887,20 +887,20 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.101167315175097</v>
+        <v>0.1475409836065575</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>13.46153846153846</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>66.02564102564102</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
     <row r="9">
@@ -929,20 +929,20 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1475409836065573</v>
+        <v>0.3715675057208238</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>16.02564102564103</v>
+        <v>37.82051282051282</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>65.38461538461539</v>
+        <v>46.7948717948718</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>18.58974358974359</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="10">
@@ -971,20 +971,20 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1874576800875045</v>
+        <v>0.1415457506662717</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>48.71794871794872</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>19.87179487179487</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
     <row r="11">
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>34.61538461538461</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>34.61538461538461</v>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>34.61538461538461</v>
@@ -1265,20 +1265,20 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.1593744508873661</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>53.2051282051282</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>26.28205128205128</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
     <row r="18">
@@ -1307,20 +1307,20 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.183690112130479</v>
+        <v>0.3300341296928327</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>55.12820512820513</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>26.92307692307692</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>17.94871794871795</v>
+        <v>14.1025641025641</v>
       </c>
     </row>
     <row r="19">
@@ -1349,20 +1349,20 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1399627868513541</v>
+        <v>0.1480694296847326</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>58.97435897435898</v>
+        <v>49.35897435897436</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>10.8974358974359</v>
+        <v>17.30769230769231</v>
       </c>
     </row>
     <row r="20">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>35.25641025641026</v>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>35.25641025641026</v>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>35.25641025641026</v>
@@ -1643,20 +1643,20 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.129032258064516</v>
+        <v>0.1885350318471336</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>24.35897435897436</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1343921808185706</v>
+        <v>0.2358414601413615</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>34.61538461538461</v>
+        <v>22.43589743589744</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>41.66666666666667</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>23.71794871794872</v>
+        <v>19.87179487179487</v>
       </c>
     </row>
     <row r="28">
@@ -1727,20 +1727,20 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.03849388022049882</v>
+        <v>0.04882251579551988</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>19.23076923076923</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>46.7948717948718</v>
+        <v>48.07692307692308</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>33.97435897435898</v>
+        <v>31.41025641025641</v>
       </c>
     </row>
     <row r="29">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>32.05128205128205</v>
@@ -1937,17 +1937,17 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>32.05128205128205</v>
@@ -1979,17 +1979,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="J34" s="5" t="n">
         <v>32.05128205128205</v>
@@ -2021,20 +2021,20 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1207547169811322</v>
+        <v>0.1576302565458875</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>26.92307692307692</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>48.71794871794872</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>24.35897435897436</v>
+        <v>26.92307692307692</v>
       </c>
     </row>
     <row r="36">
@@ -2063,20 +2063,20 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.1367911085779425</v>
+        <v>0.2406940381317463</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>25</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>51.28205128205128</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>23.71794871794872</v>
+        <v>18.58974358974359</v>
       </c>
     </row>
     <row r="37">
@@ -2105,20 +2105,20 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.0104233689357871</v>
+        <v>0.03285802851828901</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>16.02564102564103</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>47.43589743589743</v>
+        <v>42.94871794871795</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>36.53846153846153</v>
+        <v>30.12820512820513</v>
       </c>
     </row>
   </sheetData>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>25.64102564102564</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>25.64102564102564</v>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>25.64102564102564</v>
@@ -2410,20 +2410,20 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.101167315175097</v>
+        <v>0.1475409836065575</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>13.46153846153846</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>66.02564102564102</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
     <row r="12">
@@ -2442,20 +2442,20 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1475409836065573</v>
+        <v>0.3715675057208238</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>16.02564102564103</v>
+        <v>37.82051282051282</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>65.38461538461539</v>
+        <v>46.7948717948718</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>18.58974358974359</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="13">
@@ -2474,20 +2474,20 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>163 / 207</t>
+          <t>107 / 184</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1874576800875045</v>
+        <v>0.1415457506662717</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>48.71794871794872</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>19.87179487179487</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
   </sheetData>
@@ -2691,13 +2691,13 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>34.61538461538461</v>
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>34.61538461538461</v>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>34.61538461538461</v>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.1593744508873661</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>53.2051282051282</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>26.28205128205128</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
     </row>
     <row r="12">
@@ -2815,20 +2815,20 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.183690112130479</v>
+        <v>0.3300341296928327</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>55.12820512820513</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26.92307692307692</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>17.94871794871795</v>
+        <v>14.1025641025641</v>
       </c>
     </row>
     <row r="13">
@@ -2847,20 +2847,20 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1,000,000 / 36,470,000</t>
+          <t>1,750,000 / 15,000,000</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1399627868513541</v>
+        <v>0.1480694296847326</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>58.97435897435898</v>
+        <v>49.35897435897436</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>10.8974358974359</v>
+        <v>17.30769230769231</v>
       </c>
     </row>
   </sheetData>
@@ -3064,13 +3064,13 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>35.25641025641026</v>
@@ -3096,13 +3096,13 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>35.25641025641026</v>
@@ -3128,13 +3128,13 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>35.25641025641026</v>
@@ -3156,20 +3156,20 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.129032258064516</v>
+        <v>0.1885350318471336</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>37.82051282051282</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>37.82051282051282</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>24.35897435897436</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -3188,20 +3188,20 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1343921808185706</v>
+        <v>0.2358414601413615</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>34.61538461538461</v>
+        <v>22.43589743589744</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>41.66666666666667</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>23.71794871794872</v>
+        <v>19.87179487179487</v>
       </c>
     </row>
     <row r="13">
@@ -3220,20 +3220,20 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>3 / 75</t>
+          <t>31.36 / 74.23</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.03849388022049882</v>
+        <v>0.04882251579551988</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>19.23076923076923</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>46.7948717948718</v>
+        <v>48.07692307692308</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>33.97435897435898</v>
+        <v>31.41025641025641</v>
       </c>
     </row>
   </sheetData>
@@ -3433,17 +3433,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>32.05128205128205</v>
@@ -3465,17 +3465,17 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>32.05128205128205</v>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,260,000 / 3,600,000</t>
+          <t>1,260,000 / 2,832,000</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>32.05128205128205</v>
@@ -3529,20 +3529,20 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1207547169811322</v>
+        <v>0.1576302565458875</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>26.92307692307692</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>48.71794871794872</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>24.35897435897436</v>
+        <v>26.92307692307692</v>
       </c>
     </row>
     <row r="12">
@@ -3561,20 +3561,20 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1367911085779425</v>
+        <v>0.2406940381317463</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>25</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>51.28205128205128</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>23.71794871794872</v>
+        <v>18.58974358974359</v>
       </c>
     </row>
     <row r="13">
@@ -3593,20 +3593,20 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>225,000 / 1,740,000</t>
+          <t>1,612,000 / 8,000,000</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.0104233689357871</v>
+        <v>0.03285802851828901</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>16.02564102564103</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>47.43589743589743</v>
+        <v>42.94871794871795</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>36.53846153846153</v>
+        <v>30.12820512820513</v>
       </c>
     </row>
   </sheetData>
@@ -3844,13 +3844,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>74.35897435897436</v>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>74.35897435897436</v>
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.3089644310276939</v>
+        <v>0.3020998415213946</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>35.8974358974359</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>38.46153846153847</v>
+        <v>39.1025641025641</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>74.35897435897436</v>
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.101167315175097</v>
+        <v>0.1475409836065575</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>13.46153846153846</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>66.02564102564102</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>79.48717948717949</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>79.48717948717949</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="J8" s="13" t="n">
         <v>100</v>
@@ -4016,22 +4016,22 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.1475409836065573</v>
+        <v>0.3715675057208238</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>16.02564102564103</v>
+        <v>37.82051282051282</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>65.38461538461539</v>
+        <v>46.7948717948718</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>81.41025641025641</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>81.41025641025641</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>18.58974358974359</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="J9" s="13" t="n">
         <v>100</v>
@@ -4059,22 +4059,22 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.1874576800875045</v>
+        <v>0.1415457506662717</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>48.71794871794872</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>80.12820512820514</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>80.12820512820512</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>19.87179487179487</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="J10" s="13" t="n">
         <v>100</v>
@@ -4231,13 +4231,13 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>65.38461538461539</v>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>65.38461538461539</v>
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0.213931262635545</v>
+        <v>0.2081218274111676</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>33.97435897435898</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>65.38461538461539</v>
@@ -4360,22 +4360,22 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.1593744508873661</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>53.2051282051282</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>26.28205128205128</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>79.48717948717949</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>79.48717948717949</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>20.51282051282051</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="J17" s="13" t="n">
         <v>100</v>
@@ -4403,22 +4403,22 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.183690112130479</v>
+        <v>0.3300341296928327</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>55.12820512820513</v>
+        <v>45.51282051282051</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>26.92307692307692</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>82.05128205128204</v>
+        <v>85.8974358974359</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>82.05128205128206</v>
+        <v>85.8974358974359</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>17.94871794871795</v>
+        <v>14.1025641025641</v>
       </c>
       <c r="J18" s="13" t="n">
         <v>100</v>
@@ -4446,22 +4446,22 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.1399627868513541</v>
+        <v>0.1480694296847326</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>58.97435897435898</v>
+        <v>49.35897435897436</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>89.1025641025641</v>
+        <v>82.69230769230769</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>89.1025641025641</v>
+        <v>82.69230769230769</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>10.8974358974359</v>
+        <v>17.30769230769231</v>
       </c>
       <c r="J19" s="13" t="n">
         <v>100</v>
@@ -4618,19 +4618,19 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>64.74358974358975</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>64.74358974358974</v>
+        <v>64.74358974358975</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>35.25641025641026</v>
@@ -4661,19 +4661,19 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>64.74358974358975</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>64.74358974358974</v>
+        <v>64.74358974358975</v>
       </c>
       <c r="I24" s="13" t="n">
         <v>35.25641025641026</v>
@@ -4704,19 +4704,19 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.2635935724720014</v>
+        <v>0.2627719384013689</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>33.33333333333333</v>
+        <v>33.97435897435898</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>31.41025641025641</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>64.74358974358975</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>64.74358974358974</v>
+        <v>64.74358974358975</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>35.25641025641026</v>
@@ -4747,22 +4747,22 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.129032258064516</v>
+        <v>0.1885350318471336</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>37.82051282051282</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>37.82051282051282</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>75.64102564102564</v>
+        <v>75</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>75.64102564102564</v>
+        <v>75</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>24.35897435897436</v>
+        <v>25</v>
       </c>
       <c r="J26" s="13" t="n">
         <v>100</v>
@@ -4790,22 +4790,22 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.1343921808185706</v>
+        <v>0.2358414601413615</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>34.61538461538461</v>
+        <v>22.43589743589744</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>41.66666666666667</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>76.28205128205127</v>
+        <v>80.12820512820514</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>76.28205128205128</v>
+        <v>80.12820512820512</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>23.71794871794872</v>
+        <v>19.87179487179487</v>
       </c>
       <c r="J27" s="13" t="n">
         <v>100</v>
@@ -4833,22 +4833,22 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>-0.03849388022049882</v>
+        <v>0.04882251579551988</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>19.23076923076923</v>
+        <v>20.51282051282051</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>46.7948717948718</v>
+        <v>48.07692307692308</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>66.02564102564102</v>
+        <v>68.58974358974359</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>66.02564102564102</v>
+        <v>68.58974358974359</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>33.97435897435898</v>
+        <v>31.41025641025641</v>
       </c>
       <c r="J28" s="13" t="n">
         <v>100</v>
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>67.94871794871796</v>
@@ -5048,13 +5048,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>67.94871794871796</v>
@@ -5091,13 +5091,13 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.2162722404560374</v>
+        <v>0.2236481861738536</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>30.12820512820513</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>37.82051282051282</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>67.94871794871796</v>
@@ -5134,22 +5134,22 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.1207547169811322</v>
+        <v>0.1576302565458875</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>26.92307692307692</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>48.71794871794872</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>75.64102564102564</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>75.64102564102564</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>24.35897435897436</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="J35" s="13" t="n">
         <v>100</v>
@@ -5177,25 +5177,25 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>0.1367911085779425</v>
+        <v>0.2406940381317463</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>25</v>
+        <v>35.25641025641026</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>51.28205128205128</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>76.28205128205127</v>
+        <v>81.41025641025641</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>76.28205128205127</v>
+        <v>81.41025641025641</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>23.71794871794872</v>
+        <v>18.58974358974359</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -5220,25 +5220,25 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>-0.0104233689357871</v>
+        <v>0.03285802851828901</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>16.02564102564103</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>47.43589743589743</v>
+        <v>42.94871794871795</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>63.46153846153846</v>
+        <v>69.87179487179486</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>63.46153846153845</v>
+        <v>69.87179487179488</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>36.53846153846153</v>
+        <v>30.12820512820513</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -5317,154 +5317,189 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Weighted_Hazard = 0.35*Norm_Wind Gust + 0.35*Norm_Rainfall + 0.30*Norm_Storm Surge</t>
+          <t>Weighted_Hazard = w_wind*Norm_Wind Gust + w_rain*Norm_Rainfall + w_surge*Norm_Storm Surge</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Equivalent Excel columns: 0.35*H + 0.35*J + 0.30*L.</t>
+          <t>Equivalent Excel columns: w_wind*H + w_rain*J + w_surge*L.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr"/>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Weights used for Sitrang (see HAZARD_WEIGHTS in the script):</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Forecast severity boundaries:</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1dlt: w_wind=0.4, w_rain=0.2, w_surge=0.4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Derived independently for each lead exactly as in the repository.</t>
+          <t xml:space="preserve">  2dlt: w_wind=0.4, w_rain=0.2, w_surge=0.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>House: from Norm_Impact_House using Excel AG class labels.</t>
+          <t xml:space="preserve">  3dlt: w_wind=0.5, w_rain=0.5, w_surge=0.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Agriculture: from Norm_Impact_fAPAR using Excel X class labels.</t>
+          <t>Weights differ by cyclone and by lead time and are set manually in HAZARD_WEIGHTS.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Thresholds are rounded to 4 decimals before classification.</t>
-        </is>
-      </c>
+      <c r="A17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>The same lead-specific sector boundary set is applied to Composite, Vulnerability-only and Hazard-only.</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Forecast severity boundaries:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr"/>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Derived independently for each lead exactly as in the repository.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>DDM calibration:</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>House: from Norm_Impact_House using Excel AG class labels.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Zero = No Impact.</t>
+          <t>Agriculture: from Norm_Impact_fAPAR using Excel X class labels.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Positive DDM values are exhaustively searched for Low/High cut pairs.</t>
+          <t>Thresholds are rounded to 4 decimals before classification.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>For each candidate pair, QWK is calculated separately for 1dlt, 2dlt and 3dlt.</t>
+          <t>The same lead-specific sector boundary set is applied to Composite, Vulnerability-only and Hazard-only.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>The mean of the three Kappas is maximized.</t>
-        </is>
-      </c>
+      <c r="A24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>The selected Low/High pair is then fixed for all three leads for that predictor and damage variable.</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>DDM calibration:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>The maximum positive observed DDM value is excluded as a High cut so that the High class remains populated.</t>
+          <t>Zero = No Impact.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr"/>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Positive DDM values are exhaustively searched for Low/High cut pairs.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Agreement table:</t>
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>For each candidate pair, QWK is calculated separately for 1dlt, 2dlt and 3dlt.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Exact = difference of 0 classes.</t>
+          <t>The mean of the three Kappas is maximized.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Adjacent = difference of exactly 1 class.</t>
+          <t>The selected Low/High pair is then fixed for all three leads for that predictor and damage variable.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>The maximum positive observed DDM value is excluded as a High cut so that the High class remains populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Agreement table:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Exact = difference of 0 classes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Adjacent = difference of exactly 1 class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
           <t>Off-Cat. = difference of 2 or more classes.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Exact + Adjacent + Off-Cat. = 100%.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Repository Within-1 % = Exact % + Adjacent %.</t>
         </is>
